--- a/projects.xlsx
+++ b/projects.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naumann\Dropbox (Privat)\lennardnau.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184FC822-DEE1-41FD-8996-64715A7CAF62}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C758FF5E-E6B6-497C-A65E-322039A6C544}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12600" windowHeight="8484" xr2:uid="{3CBB864D-7064-4EC0-B319-6895944E5474}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12600" windowHeight="8490" xr2:uid="{3CBB864D-7064-4EC0-B319-6895944E5474}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -93,9 +93,6 @@
     <t>https://osf.io/download/4aqxm/</t>
   </si>
   <si>
-    <t>Recent meta-analyses suggest that, while contact can reduce prejudice, its effects are on average small, especially in well-powered field experimental studies with delayed outcome measurement. One of the reasons why intergroup contact may fail to produce larger effect sizes is that individuals prone to avoiding outgroup contact are both less likely to benefit from and less likely to engage in such encounters. Yet, research on the drivers of intergroup avoidance is scarce. In this study, I systematically investigate patterns and drivers of intergroup avoidance in an online dating context. In partnership with large European online dating platform, I first analyze user data to examine the extent and covariates of ethnic bias in swiping behavior. Next, users will be randomly assigned to one of three brief video treatments that are delivered on the platform and designed to test three psychological mechanism that potentially drive intergroup avoidance. Behavioral data is complemented by an endline survey, including measures on intergroup contact preference, intent, and behavior.</t>
-  </si>
-  <si>
     <t>Intergroup contact and avoidance</t>
   </si>
   <si>
@@ -178,6 +175,9 @@
   </si>
   <si>
     <t>Intergroup contact and empathy education are widely believed to foster trust, tolerance and cooperation across group lines in deeply divided societies. We test these approaches independently and jointly in the context of refugee-host relations in Lebanon, where Syrian refugees comprise a quarter of the population. Our study embeds a popular existing family psycho-social support (FPSS) program targeting vulnerable youth in a field experiment, where Syrian and Lebanese youth were randomly assigned to either heterogeneous (Lebanese-Syrian) or homogeneous (Lebanese or Syrian) FPSS groups and to an empathy education or placebo curriculum focused on physical health and nutrition. We find that contact does not meaningfully change attitudes toward the outgroup, and has little effect on participation in future contact, such as attending events celebrating the outgroup's culture 1-2 months after treatment. By contrast, we find that empathy education consistently improves both affect and policy attitudes toward the outgroup, and has positive behavioral effects. We find no evidence of positive interaction effects between the two treatments. In fact, combining contact and empathy training is less effective than either treatment alone. Our study points to empathy education as a cheaper, more scalable, and potentially more effective strategy for building social cohesion in conflict settings than intergroup contact.</t>
+  </si>
+  <si>
+    <t>Recent meta-analyses suggest that, while contact can reduce prejudice, the effects are small, particularly in well-powered field experimental studies with delayed outcome measurement. One reason intergroup contact may fail to produce larger effect sizes is that those prone to avoiding outgroup contact are less likely to benefit from or engage in such encounters. However, research into the drivers of intergroup avoidance is scarce. In this study, I systematically investigate the patterns and drivers of intergroup avoidance in an online dating context. In partnership with a large European online dating platform, I first analyse user data to examine the extent  and covariates of ethnic bias in swiping behavior. Next, I conduct a large-scale field RCT in which users are randomly assigned to one of three brief video treatments. They delivered on the platform and designed to test three psychological mechanisms that potentially drive intergroup avoidance: ingroup norms, outgroup norms, and perceived group commonality. Behavioral swiping data is complemented by an endline survey including measures of intergroup contact preference, intent, and behavior.</t>
   </si>
 </sst>
 </file>
@@ -537,9 +537,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D89CD754-C723-407F-815A-E294119BEA7C}">
   <dimension ref="A1:K8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -562,7 +562,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
         <v>18</v>
@@ -571,33 +571,33 @@
         <v>19</v>
       </c>
       <c r="K1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="H2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I2" t="s">
         <v>20</v>
@@ -606,117 +606,117 @@
         <v>21</v>
       </c>
       <c r="K2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" t="s">
         <v>37</v>
       </c>
+      <c r="J3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
         <v>39</v>
       </c>
-      <c r="K3" t="s">
-        <v>37</v>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>30</v>
       </c>
-      <c r="H4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" t="s">
-        <v>37</v>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -728,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F6">
         <v>2022</v>
@@ -740,53 +740,53 @@
         <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
         <v>41</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>43</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>44</v>
       </c>
       <c r="F7">
         <v>2024</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -810,13 +810,13 @@
         <v>14</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/projects.xlsx
+++ b/projects.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naumann\Dropbox (Privat)\lennardnau.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C758FF5E-E6B6-497C-A65E-322039A6C544}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3D03A8-E6D4-421E-857B-9B54A7EF1009}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12600" windowHeight="8490" xr2:uid="{3CBB864D-7064-4EC0-B319-6895944E5474}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12600" windowHeight="8496" xr2:uid="{3CBB864D-7064-4EC0-B319-6895944E5474}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
   <si>
     <t>category</t>
   </si>
@@ -36,15 +36,9 @@
     <t>authors</t>
   </si>
   <si>
-    <t>author_links</t>
-  </si>
-  <si>
     <t>journal</t>
   </si>
   <si>
-    <t>year</t>
-  </si>
-  <si>
     <t>abstract</t>
   </si>
   <si>
@@ -54,27 +48,18 @@
     <t>Christoph Trinn</t>
   </si>
   <si>
-    <t>https://www.uni-heidelberg.de/politikwissenschaften/personal/trinn.html</t>
-  </si>
-  <si>
     <t>https://journals.sagepub.com/doi/full/10.1177/07388942221092126</t>
   </si>
   <si>
     <t>Attributing agnostically detected large reductions in road CO2 emissions to policy mixes</t>
   </si>
   <si>
-    <t>Nature Energy 7</t>
-  </si>
-  <si>
     <t>Policymakers combine many different policy tools to achieve emission reductions. However, there remains substantial uncertainty around which mixes of policies are effective. This uncertainty stems from the predominant focus of ex post policy evaluation on isolating effects of single, known policies. Here we introduce an approach to identify effective policy interventions in the EU road transport sector by detecting treatment effects as structural breaks in CO2 emissions that can potentially occur in any country at any point in time from any number of a priori unknown policies. This search for ‘causes of effects’ within a statistical framework allows us to draw systematic inference on the effectiveness of policy mixes. We detect ten successful policy interventions that reduced emissions between 8% and 26%. The most successful policy mixes combine carbon or fuel taxes with green vehicle incentives and highlight that emissions reductions on a magnitude that matches the EU zero emission targets are possible.</t>
   </si>
   <si>
     <t>https://www.nature.com/articles/s41560-022-01095-6</t>
   </si>
   <si>
-    <t>https://www.pik-potsdam.de/members/nicolask, https://felixpretis.climateeconometrics.org/, https://www.pik-potsdam.de/members/ritter/homepage, https://www.moritzschwarz.org/</t>
-  </si>
-  <si>
     <t>Nicolas Koch, Felix Pretis, Nolan Ritter, Moritz Schwarz</t>
   </si>
   <si>
@@ -93,9 +78,6 @@
     <t>https://osf.io/download/4aqxm/</t>
   </si>
   <si>
-    <t>Intergroup contact and avoidance</t>
-  </si>
-  <si>
     <t>Outgroup Avoidance in Online Dating: Evidence from a Large-Scale Field Experiment</t>
   </si>
   <si>
@@ -105,9 +87,6 @@
     <t>Salma Mousa, Alex Scacco</t>
   </si>
   <si>
-    <t>https://www.salmamousa.com/, https://sites.google.com/view/alex-scacco/</t>
-  </si>
-  <si>
     <t>“Native Flight” in Urban School Districts? Evidence from Primary School Registration Data in Berlin</t>
   </si>
   <si>
@@ -117,24 +96,15 @@
     <t>We investigate parental school choice in Berlin, Germany. Anecdotal evidence suggests that nonmigrant “natives” take steps to avoid or seek out catchment area schools due to the ethnic composition of student bodies. Indeed, school segregation has been documented across Europe, but the lack of high-resolution data on school choice and migrant populations has made it difficult to precisely show the extent to which schools are more (or less) segregated than we would expect given catchment area demographics and to analyze the process that leads to such segregation. We contribute to this debate with an analysis of a never-before-used dataset of 35,000 school choice forms that parents must complete to enroll their child in elementary school. We combine this data with a newly compiled set of administrative data covering Berlin’s several hundred elementary school enrollment zones for the years 2000 to 2018, which includes demographic and socioeconomic zone characteristics, student population indicators, and various school attributes and performance metrics. We explore in particular the extent to which we see Schelling sorting, where even weak preferences for separation from another group (and small changes in zone composition) can dynamically spiral to produce extreme patterns of segregation, and we develop policy implications for how to counteract such dynamics.</t>
   </si>
   <si>
-    <t>LLM and webscraping</t>
-  </si>
-  <si>
     <t>Political Connections: Measuring Political and Business Elite Networks</t>
   </si>
   <si>
     <t>Lisa Garbe, Yuequan Guo, Macartan Humphreys</t>
   </si>
   <si>
-    <t>https://www.wzb.eu/de/personen/lisa-garbe, https://yuequanguo.com/, https://macartan.github.io/</t>
-  </si>
-  <si>
     <t>Elite connections shape political and economic outcomes but are difficult to measure. Traditional methods rely on surveys or shared affiliations, which lack scalability and clear interpretation. We propose a scalable, interpretable approach to map elite networks by compiling elite lists, detecting co-appearances in media, coding interactions with large language models (LLMs), and constructing network ties. This complements conventional methods and suits dynamic elite politics. Applied to Germany (2013–2023), our data includes 750 parliamentarians and 1,051 top executives. We collected 42,366 articles from 30 newspapers, identifying co-appearances. Open-source LLMs code interactions such as meetings or conversations, enabling nuanced network definitions. We validate networks qualitatively and quantitatively by linking them to events like elections and comparing them with education-based networks. This method expands elite network research beyond typical scopes, offering scalable, interpretable insights into how political and economic elites connect and influence each other.</t>
   </si>
   <si>
-    <t>article</t>
-  </si>
-  <si>
     <t>.</t>
   </si>
   <si>
@@ -144,40 +114,55 @@
     <t>https://osf.io/6gukj</t>
   </si>
   <si>
-    <t>https://www.rwi-essen.de/en/rwi/team/person/bernd-beber, #, https://macartan.github.io/</t>
-  </si>
-  <si>
     <t>Towards Genuine Collaboration in International Research</t>
   </si>
   <si>
-    <t>https://www.wzb.eu/de/personen/nora-chirikure</t>
-  </si>
-  <si>
     <t>Nora Chirikure</t>
   </si>
   <si>
-    <t>WZB Mitteilungen 184</t>
-  </si>
-  <si>
     <t>Researchers worldwide continue to face significantly unequal starting opportunities, particularly in terms of research funding, academic career paths, visas, and networking. Nora Chirikure and Lennard Naumann explore what is needed to establish truly equitable South-North research partnerships and to ensure the success of research originating from the Global South.</t>
   </si>
   <si>
-    <t>blog</t>
-  </si>
-  <si>
     <t>https://www.wzb.eu/en/article/imbalance-of-power</t>
   </si>
   <si>
-    <t>Conflict Management and Peace Science, 40(4)</t>
-  </si>
-  <si>
-    <t>Other work</t>
-  </si>
-  <si>
     <t>Intergroup contact and empathy education are widely believed to foster trust, tolerance and cooperation across group lines in deeply divided societies. We test these approaches independently and jointly in the context of refugee-host relations in Lebanon, where Syrian refugees comprise a quarter of the population. Our study embeds a popular existing family psycho-social support (FPSS) program targeting vulnerable youth in a field experiment, where Syrian and Lebanese youth were randomly assigned to either heterogeneous (Lebanese-Syrian) or homogeneous (Lebanese or Syrian) FPSS groups and to an empathy education or placebo curriculum focused on physical health and nutrition. We find that contact does not meaningfully change attitudes toward the outgroup, and has little effect on participation in future contact, such as attending events celebrating the outgroup's culture 1-2 months after treatment. By contrast, we find that empathy education consistently improves both affect and policy attitudes toward the outgroup, and has positive behavioral effects. We find no evidence of positive interaction effects between the two treatments. In fact, combining contact and empathy training is less effective than either treatment alone. Our study points to empathy education as a cheaper, more scalable, and potentially more effective strategy for building social cohesion in conflict settings than intergroup contact.</t>
   </si>
   <si>
     <t>Recent meta-analyses suggest that, while contact can reduce prejudice, the effects are small, particularly in well-powered field experimental studies with delayed outcome measurement. One reason intergroup contact may fail to produce larger effect sizes is that those prone to avoiding outgroup contact are less likely to benefit from or engage in such encounters. However, research into the drivers of intergroup avoidance is scarce. In this study, I systematically investigate the patterns and drivers of intergroup avoidance in an online dating context. In partnership with a large European online dating platform, I first analyse user data to examine the extent  and covariates of ethnic bias in swiping behavior. Next, I conduct a large-scale field RCT in which users are randomly assigned to one of three brief video treatments. They delivered on the platform and designed to test three psychological mechanisms that potentially drive intergroup avoidance: ingroup norms, outgroup norms, and perceived group commonality. Behavioral swiping data is complemented by an endline survey including measures of intergroup contact preference, intent, and behavior.</t>
+  </si>
+  <si>
+    <t>Dissertation chapters</t>
+  </si>
+  <si>
+    <t>Chatting Across Divides: LLMs as Agents of Depolarization?</t>
+  </si>
+  <si>
+    <t>Affective polarization, understood as animosity and avoidance between opposing partisans, is a growing concern for democratic societies. This paper tests whether brief interactions with an instructed large language model chatbot can reduce out-partisan animosity and avoidance. In a pre-registered 2 × 2 factorial Experiment with a representative German sample (N ≈ 1,600 and a one-week follow-up), re-spondents were randomly assigned to discuss a polarizing political issue with a value-based chatbot, a perspective-taking chatbot, both in sequence, or neither. The value-based chatbot increases self-reported real-world political discussions with outpartisans at follow-up, and both chatbots raise stated willingness to participate in future outpartisan conversations, though the latter outcome is difficult to cleanly interpret. The chatbots have tightly estimated null effects on outpartisan affect, avoidant preferences, and durable attitude change toward the bot’s position.</t>
+  </si>
+  <si>
+    <t>https://osf.io/mytu9/</t>
+  </si>
+  <si>
+    <t>https://osf.io/mytu9/files/ybnjv</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>Policy and outreach</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>Conflict Management and Peace Science, 40(4), 2022.</t>
+  </si>
+  <si>
+    <t>WZB Mitteilungen 184, 2024.</t>
+  </si>
+  <si>
+    <t>Nature Energy 7, 2022.</t>
   </si>
 </sst>
 </file>
@@ -536,10 +521,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D89CD754-C723-407F-815A-E294119BEA7C}">
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -556,267 +541,221 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="C7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E9" t="s">
         <v>9</v>
       </c>
-      <c r="E6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6">
-        <v>2022</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="I6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7">
-        <v>2024</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8">
-        <v>2022</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K8" t="s">
-        <v>36</v>
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/projects.xlsx
+++ b/projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naumann\Dropbox (Privat)\lennardnau.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3D03A8-E6D4-421E-857B-9B54A7EF1009}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AC23B1-2F90-4986-9660-0B7E0F019B3C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="12600" windowHeight="8496" xr2:uid="{3CBB864D-7064-4EC0-B319-6895944E5474}"/>
   </bookViews>
@@ -138,9 +138,6 @@
     <t>Chatting Across Divides: LLMs as Agents of Depolarization?</t>
   </si>
   <si>
-    <t>Affective polarization, understood as animosity and avoidance between opposing partisans, is a growing concern for democratic societies. This paper tests whether brief interactions with an instructed large language model chatbot can reduce out-partisan animosity and avoidance. In a pre-registered 2 × 2 factorial Experiment with a representative German sample (N ≈ 1,600 and a one-week follow-up), re-spondents were randomly assigned to discuss a polarizing political issue with a value-based chatbot, a perspective-taking chatbot, both in sequence, or neither. The value-based chatbot increases self-reported real-world political discussions with outpartisans at follow-up, and both chatbots raise stated willingness to participate in future outpartisan conversations, though the latter outcome is difficult to cleanly interpret. The chatbots have tightly estimated null effects on outpartisan affect, avoidant preferences, and durable attitude change toward the bot’s position.</t>
-  </si>
-  <si>
     <t>https://osf.io/mytu9/</t>
   </si>
   <si>
@@ -163,6 +160,9 @@
   </si>
   <si>
     <t>Nature Energy 7, 2022.</t>
+  </si>
+  <si>
+    <t>Affective polarization, understood as animosity and avoidance between opposing partisans, is a growing concern for democratic societies. This paper tests whether brief interactions with an instructed large language model chatbot can reduce out-partisan animosity and avoidance. In a pre-registered 2 × 2 factorial Experiment with a representative German sample (N ≈ 1,600 and a one-week follow-up), re-spondents were randomly assigned to discuss a polarizing political issue with a value-based chatbot, a perspective-taking chatbot, both in sequence, or neither. The value-based chatbot increases self-reported real-world political discussions with outpartisans at follow-up, and both chatbots raise stated willingness to participate in future outpartisan conversations. The chatbots have tightly estimated null effects on outpartisan affect, avoidant preferences, and durable attitude change toward the bot’s position.</t>
   </si>
 </sst>
 </file>
@@ -541,7 +541,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s">
         <v>13</v>
@@ -616,21 +616,21 @@
         <v>26</v>
       </c>
       <c r="E4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
         <v>37</v>
       </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>38</v>
-      </c>
-      <c r="H4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -656,7 +656,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -682,7 +682,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
@@ -691,7 +691,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>12</v>
@@ -708,7 +708,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
@@ -717,7 +717,7 @@
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>31</v>
@@ -734,7 +734,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -743,7 +743,7 @@
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>

--- a/projects.xlsx
+++ b/projects.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naumann\Dropbox (Privat)\lennardnau.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AC23B1-2F90-4986-9660-0B7E0F019B3C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44EF24A8-0A9F-42D1-A9C1-158C0896FAF3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12600" windowHeight="8496" xr2:uid="{3CBB864D-7064-4EC0-B319-6895944E5474}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12600" windowHeight="8500" xr2:uid="{3CBB864D-7064-4EC0-B319-6895944E5474}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -78,12 +78,6 @@
     <t>https://osf.io/download/4aqxm/</t>
   </si>
   <si>
-    <t>Outgroup Avoidance in Online Dating: Evidence from a Large-Scale Field Experiment</t>
-  </si>
-  <si>
-    <t>Intergroup Contact, Empathy Education, and Refugee-Native Integration: Evidence from a Field Experiment in Lebanon</t>
-  </si>
-  <si>
     <t>Salma Mousa, Alex Scacco</t>
   </si>
   <si>
@@ -163,6 +157,12 @@
   </si>
   <si>
     <t>Affective polarization, understood as animosity and avoidance between opposing partisans, is a growing concern for democratic societies. This paper tests whether brief interactions with an instructed large language model chatbot can reduce out-partisan animosity and avoidance. In a pre-registered 2 × 2 factorial Experiment with a representative German sample (N ≈ 1,600 and a one-week follow-up), re-spondents were randomly assigned to discuss a polarizing political issue with a value-based chatbot, a perspective-taking chatbot, both in sequence, or neither. The value-based chatbot increases self-reported real-world political discussions with outpartisans at follow-up, and both chatbots raise stated willingness to participate in future outpartisan conversations. The chatbots have tightly estimated null effects on outpartisan affect, avoidant preferences, and durable attitude change toward the bot’s position.</t>
+  </si>
+  <si>
+    <t>Outgroup Avoidance in Online Dating: Evidence from a Field Experiment</t>
+  </si>
+  <si>
+    <t>Intergroup Contact, Empathy Education, and Refugee-Native Integration in Lebanon</t>
   </si>
 </sst>
 </file>
@@ -522,9 +522,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D89CD754-C723-407F-815A-E294119BEA7C}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -541,7 +541,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
         <v>13</v>
@@ -550,50 +550,50 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>33</v>
       </c>
-      <c r="F2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -602,87 +602,87 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
         <v>35</v>
       </c>
-      <c r="B4" t="s">
+      <c r="H4" t="s">
         <v>36</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>37</v>
       </c>
-      <c r="H4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>39</v>
-      </c>
       <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="F5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
@@ -691,7 +691,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>12</v>
@@ -700,41 +700,41 @@
         <v>7</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" t="s">
         <v>30</v>
       </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -743,7 +743,7 @@
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -752,10 +752,10 @@
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
